--- a/Nov_Erection_Summary.xlsx
+++ b/Nov_Erection_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,20 +456,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Week 5</t>
+          <t>Avg Productivity (MTD)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avg Productivity (MTD)</t>
+          <t>Total MT (For this month) (MTD)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Total MT (For this month) (MTD)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Total No. of Erections (For this month) (MTD)</t>
         </is>
@@ -482,28 +477,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="C2" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="D2" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="E2" t="n">
-        <v>4.75</v>
+        <v>4.86</v>
       </c>
       <c r="F2" t="n">
-        <v>5.03</v>
+        <v>4.44</v>
       </c>
       <c r="G2" t="n">
-        <v>4.43</v>
+        <v>3748.82</v>
       </c>
       <c r="H2" t="n">
-        <v>2913.51</v>
-      </c>
-      <c r="I2" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
@@ -513,28 +505,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.72</v>
+        <v>4.67</v>
       </c>
       <c r="C3" t="n">
-        <v>4.83</v>
+        <v>4.67</v>
       </c>
       <c r="D3" t="n">
-        <v>4.86</v>
+        <v>4.64</v>
       </c>
       <c r="E3" t="n">
-        <v>5.21</v>
+        <v>4.91</v>
       </c>
       <c r="F3" t="n">
-        <v>5.81</v>
+        <v>4.57</v>
       </c>
       <c r="G3" t="n">
-        <v>4.61</v>
+        <v>8757.41</v>
       </c>
       <c r="H3" t="n">
-        <v>8465.15</v>
-      </c>
-      <c r="I3" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7">
@@ -570,20 +559,15 @@
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>Week 5</t>
+          <t>Avg Productivity (MTD)</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>Avg Productivity (MTD)</t>
+          <t>Total MT (For this month) (MTD)</t>
         </is>
       </c>
       <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>Total MT (For this month) (MTD)</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="inlineStr">
         <is>
           <t>Total No. of Erections (For this month) (MTD)</t>
         </is>
@@ -601,28 +585,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="D8" t="n">
-        <v>4.49</v>
+        <v>4.59</v>
       </c>
       <c r="E8" t="n">
-        <v>3.99</v>
+        <v>4.42</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="H8" t="n">
-        <v>3.97</v>
+        <v>1429.26</v>
       </c>
       <c r="I8" t="n">
-        <v>831.35</v>
-      </c>
-      <c r="J8" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -646,18 +627,15 @@
         <v>3.96</v>
       </c>
       <c r="F9" t="n">
-        <v>4.59</v>
+        <v>4.65</v>
       </c>
       <c r="G9" t="n">
-        <v>5.03</v>
+        <v>4.16</v>
       </c>
       <c r="H9" t="n">
-        <v>4.16</v>
+        <v>646.72</v>
       </c>
       <c r="I9" t="n">
-        <v>646.72</v>
-      </c>
-      <c r="J9" t="n">
         <v>13</v>
       </c>
     </row>
@@ -676,25 +654,22 @@
         <v>4.45</v>
       </c>
       <c r="D10" t="n">
-        <v>4.97</v>
+        <v>4.68</v>
       </c>
       <c r="E10" t="n">
-        <v>5.12</v>
+        <v>4.62</v>
       </c>
       <c r="F10" t="n">
-        <v>4.91</v>
+        <v>4.96</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="H10" t="n">
-        <v>4.84</v>
+        <v>1672.84</v>
       </c>
       <c r="I10" t="n">
-        <v>1435.44</v>
-      </c>
-      <c r="J10" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -709,27 +684,24 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="D11" t="n">
-        <v>3.98</v>
+        <v>4.03</v>
       </c>
       <c r="E11" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="F11" t="n">
-        <v>4.93</v>
+        <v>4.99</v>
       </c>
       <c r="G11" t="n">
-        <v>6.13</v>
+        <v>4.29</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2</v>
+        <v>2808.11</v>
       </c>
       <c r="I11" t="n">
-        <v>2808.11</v>
-      </c>
-      <c r="J11" t="n">
         <v>38</v>
       </c>
     </row>
@@ -748,24 +720,21 @@
         <v>3.48</v>
       </c>
       <c r="D12" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="E12" t="n">
-        <v>4.12</v>
+        <v>4.45</v>
       </c>
       <c r="F12" t="n">
-        <v>4.1</v>
+        <v>4.46</v>
       </c>
       <c r="G12" t="n">
-        <v>3.74</v>
+        <v>4.06</v>
       </c>
       <c r="H12" t="n">
-        <v>3.79</v>
+        <v>962.36</v>
       </c>
       <c r="I12" t="n">
-        <v>962.36</v>
-      </c>
-      <c r="J12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -781,28 +750,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.43</v>
+        <v>3.04</v>
       </c>
       <c r="D13" t="n">
-        <v>3.76</v>
+        <v>3.26</v>
       </c>
       <c r="E13" t="n">
-        <v>3.89</v>
+        <v>3.2</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="H13" t="n">
-        <v>3.66</v>
+        <v>365</v>
       </c>
       <c r="I13" t="n">
-        <v>247</v>
-      </c>
-      <c r="J13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -826,18 +792,15 @@
         <v>6.12</v>
       </c>
       <c r="F14" t="n">
-        <v>7.29</v>
+        <v>7.49</v>
       </c>
       <c r="G14" t="n">
-        <v>9.15</v>
+        <v>6.62</v>
       </c>
       <c r="H14" t="n">
-        <v>6.62</v>
+        <v>949.77</v>
       </c>
       <c r="I14" t="n">
-        <v>949.77</v>
-      </c>
-      <c r="J14" t="n">
         <v>22</v>
       </c>
     </row>
@@ -859,21 +822,18 @@
         <v>4.45</v>
       </c>
       <c r="E15" t="n">
-        <v>4.72</v>
+        <v>4.89</v>
       </c>
       <c r="F15" t="n">
-        <v>5.17</v>
+        <v>5.37</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>324.01</v>
       </c>
       <c r="I15" t="n">
-        <v>324.01</v>
-      </c>
-      <c r="J15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -898,18 +858,15 @@
         <v>4.35</v>
       </c>
       <c r="F16" t="n">
-        <v>4.99</v>
+        <v>5.02</v>
       </c>
       <c r="G16" t="n">
-        <v>5.57</v>
+        <v>4.26</v>
       </c>
       <c r="H16" t="n">
-        <v>4.25</v>
+        <v>1501.99</v>
       </c>
       <c r="I16" t="n">
-        <v>1501.99</v>
-      </c>
-      <c r="J16" t="n">
         <v>34</v>
       </c>
     </row>
@@ -934,18 +891,15 @@
         <v>5.45</v>
       </c>
       <c r="F17" t="n">
-        <v>4.79</v>
+        <v>4.65</v>
       </c>
       <c r="G17" t="n">
-        <v>4.48</v>
+        <v>5.24</v>
       </c>
       <c r="H17" t="n">
-        <v>5.33</v>
+        <v>1564.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1564.4</v>
-      </c>
-      <c r="J17" t="n">
         <v>58</v>
       </c>
     </row>
@@ -964,25 +918,22 @@
         <v>7.48</v>
       </c>
       <c r="D18" t="n">
-        <v>6.38</v>
+        <v>5.44</v>
       </c>
       <c r="E18" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="H18" t="n">
-        <v>6.72</v>
+        <v>281.76</v>
       </c>
       <c r="I18" t="n">
-        <v>107.51</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
